--- a/notebooks/partidos_en_vivo.xlsx
+++ b/notebooks/partidos_en_vivo.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,22 +478,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Primera Division</t>
+          <t>Serie C - Girone C</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nicaragua</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jalapa</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>UNAN Managua</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -503,7 +503,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -517,117 +517,624 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Liga Profesional Argentina</t>
+          <t>Serie C - Girone C</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Gimnasia M.</t>
+          <t>Sorrento</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Instituto Cordoba</t>
+          <t>Giugliano</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="H3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Second Half</t>
+          <t>First Half</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Primera A</t>
+          <t>Serie C - Girone C</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jaguares</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Deportivo Pereira</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>81</v>
+        <v>20</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Second Half</t>
+          <t>First Half</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Serie C - Girone C</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Cavese</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SS Monopoli</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>21</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>First Half</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AGCFF Gulf Champions League</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>World</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Al Qadsia</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Zakho</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>21</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>First Half</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Cup</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Bosnia</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Zrinjski</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Stupčanica Olovo</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>17</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>First Half</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>Friendlies Clubs</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>World</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Spittal</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Pinzgau Saalfelden</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>St. Anna</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>UFC Fehring</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
         <v>2</v>
       </c>
-      <c r="G5" t="n">
-        <v>45</v>
-      </c>
-      <c r="H5" t="n">
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>19</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>First Half</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Cup</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>South-Africa</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Polokwane City</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Amazulu</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>16</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>First Half</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Cup</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>South-Africa</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SSU M-17</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Milford FC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>20</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>First Half</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AFC Champions League</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>World</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Tractor Sazi</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Al Sadd</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>62</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Second Half</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Cup</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CSKA Sofia</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CSKA 1948</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>57</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Second Half</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Liga Revelação U23</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Leixões U23</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Sporting CP U23</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>59</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Second Half</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Division 1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Saudi-Arabia</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Al Wehda Club</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Al-Faisaly FC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>64</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Second Half</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AFC Cup</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>World</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Al Zawra'a</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Al-Wasl FC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>54</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Second Half</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Cup</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Albania</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Teuta Durrës</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Egnatia Rrogozhinë</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="n">
+        <v>90</v>
+      </c>
+      <c r="H16" t="n">
         <v>3</v>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Halftime</t>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Second Half</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Friendlies Clubs</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>World</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Polessya</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>64</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Second Half</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Premier League</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Mauritania</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Nouakchott Academie</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Nouadhibou</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>58</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Second Half</t>
         </is>
       </c>
     </row>
